--- a/diseases/d026/2010-2014.xlsx
+++ b/diseases/d026/2010-2014.xlsx
@@ -8341,9 +8341,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>

--- a/diseases/d026/2010-2014.xlsx
+++ b/diseases/d026/2010-2014.xlsx
@@ -776,28 +776,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -924,28 +938,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1072,28 +1100,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1220,28 +1262,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1368,28 +1424,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1516,28 +1586,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1664,28 +1748,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -1812,28 +1910,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -1960,28 +2072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2108,28 +2234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2256,28 +2396,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2404,28 +2558,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -2552,28 +2720,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -2700,28 +2882,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -2848,28 +3044,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -2996,28 +3206,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3144,28 +3368,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3292,28 +3530,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -3440,28 +3692,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -3588,28 +3854,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -3736,28 +4016,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -3884,28 +4178,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4032,28 +4340,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -4180,28 +4502,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4328,28 +4664,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -4476,28 +4826,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -4624,28 +4988,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -4772,28 +5150,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -4920,28 +5312,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -5068,28 +5474,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5216,28 +5636,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -5364,28 +5798,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -5512,28 +5960,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -5660,28 +6122,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -5808,28 +6284,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -5956,28 +6446,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -6266,28 +6770,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6414,28 +6932,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6562,28 +7094,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -6710,28 +7256,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -6858,28 +7418,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -7006,28 +7580,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7154,28 +7742,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7302,28 +7904,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7450,28 +8066,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -7598,28 +8228,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -7746,28 +8390,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -7894,28 +8552,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8204,28 +8876,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8745,28 +9431,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -8893,28 +9593,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -9041,28 +9755,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -9189,28 +9917,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -9337,28 +10079,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -9485,28 +10241,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -9633,28 +10403,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -9781,28 +10565,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -9929,28 +10727,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -10077,28 +10889,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -10225,28 +11051,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
